--- a/results/Int Task Remove ACC -0.0/Rando_10_permute.xlsx
+++ b/results/Int Task Remove ACC -0.0/Rando_10_permute.xlsx
@@ -440,357 +440,357 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7953145173884215</v>
+        <v>0.7747027545498842</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7953145173884215</v>
+        <v>0.7742762895712139</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7940076017009104</v>
+        <v>0.7726698457045866</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7837517483144073</v>
+        <v>0.772261514554424</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7853763260095422</v>
+        <v>0.7719438525468002</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7880626926985953</v>
+        <v>0.7463676874803196</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.779849135080382</v>
+        <v>0.746876074696013</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7760740986633875</v>
+        <v>0.7468579408675053</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7760740986633875</v>
+        <v>0.7468216732104898</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7630230756167848</v>
+        <v>0.7484187301541247</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7680237455017438</v>
+        <v>0.7641567599072572</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7744313871397448</v>
+        <v>0.7745032824362991</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7846966274492402</v>
+        <v>0.7675791466945657</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7837073737693531</v>
+        <v>0.7675972805230735</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7837711621778686</v>
+        <v>0.7657094423058379</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7827637746694737</v>
+        <v>0.7657094423058379</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7781626890291617</v>
+        <v>0.7564065749422064</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7770008439697127</v>
+        <v>0.7496718843735893</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7763198653744572</v>
+        <v>0.7436638269802354</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7760860456562868</v>
+        <v>0.7413132561273139</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7763036515983797</v>
+        <v>0.7320667103016359</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7756683275831319</v>
+        <v>0.7321398856331437</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7750148697393764</v>
+        <v>0.703504650366986</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7734990950152879</v>
+        <v>0.7038041785461022</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7742250881730743</v>
+        <v>0.696352241725214</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.763397699179839</v>
+        <v>0.7003911786817859</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7571532619984076</v>
+        <v>0.7035677987580248</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.7354515493969755</v>
+        <v>0.7045389186094042</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.732546296730876</v>
+        <v>0.7099666934905102</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.7434018464930883</v>
+        <v>0.7062004039790313</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.7574152424855548</v>
+        <v>0.7014354738646731</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.7672996723963876</v>
+        <v>0.7089042644791155</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.7648940600404661</v>
+        <v>0.7092400603152471</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.7425414496651855</v>
+        <v>0.6999002852771232</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7400914627642099</v>
+        <v>0.6874139709841677</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7464084352596722</v>
+        <v>0.6673112353788008</v>
       </c>
     </row>
     <row r="38">
@@ -800,197 +800,197 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.739383603434931</v>
+        <v>0.6283469713946322</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.7175099394714138</v>
+        <v>0.5749966079073733</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.7227557360499657</v>
+        <v>0.5843914244484969</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.7301163637108383</v>
+        <v>0.5855445226024305</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.7449101543466147</v>
+        <v>0.5867789029759106</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.7333467452551238</v>
+        <v>0.5823135010406684</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.7096584184058786</v>
+        <v>0.5807808725230257</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.709867277442456</v>
+        <v>0.5836216967631329</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.7133340387748188</v>
+        <v>0.5797103366235921</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.7255502656925885</v>
+        <v>0.5992440966921336</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.7255502656925885</v>
+        <v>0.6009230758727918</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.7515172680982009</v>
+        <v>0.59122126428199</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.7512177399190847</v>
+        <v>0.5961037442729102</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.738311787500544</v>
+        <v>0.5968384843362122</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.738311787500544</v>
+        <v>0.5988895270100175</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.7344004273610032</v>
+        <v>0.5565161032663932</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.6941049270252073</v>
+        <v>0.5727143055853046</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.6924359747850182</v>
+        <v>0.5724329112346961</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.699278828307205</v>
+        <v>0.5417041788021092</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.7040324514461409</v>
+        <v>0.5342703758097288</v>
       </c>
     </row>
     <row r="58">
@@ -1000,327 +1000,327 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.7013366978340956</v>
+        <v>0.5118352031799482</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.6935139775550138</v>
+        <v>0.5345268094787441</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.6834038348140493</v>
+        <v>0.5631225770005026</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.6864259973392339</v>
+        <v>0.5637941686727659</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.6759169103710991</v>
+        <v>0.5761904538406595</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.6762345723787231</v>
+        <v>0.5744752070029859</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.6762345723787231</v>
+        <v>0.5920347264949315</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.6674763598878006</v>
+        <v>0.5920347264949315</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.6584824076262776</v>
+        <v>0.6031253760102676</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.6557704402381548</v>
+        <v>0.5931502769568961</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.6396690938973907</v>
+        <v>0.5853081428143532</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.6013670346624932</v>
+        <v>0.627485294531776</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.6020386263347565</v>
+        <v>0.5983986336053549</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5954140187721393</v>
+        <v>0.6020567601632643</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5940795823331282</v>
+        <v>0.6146712912907275</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5855827103118763</v>
+        <v>0.5302894671043817</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5823335549216064</v>
+        <v>0.4970343723519277</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5658044635672185</v>
+        <v>0.4756573619503637</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5558801392336686</v>
+        <v>0.4912891488023566</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.462813917905385</v>
+        <v>0.4928424712184141</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.4414281605983054</v>
+        <v>0.495084239100289</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.4712252409239122</v>
+        <v>0.4964280624622923</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5028858388026383</v>
+        <v>0.4980176525353652</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5024049723384447</v>
+        <v>0.4975824406511794</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5007985284718175</v>
+        <v>0.498753032616144</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5007078593292787</v>
+        <v>0.498753032616144</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5007078593292787</v>
+        <v>0.5125219419324945</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5003901973216549</v>
+        <v>0.532143171056191</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5007259931577865</v>
+        <v>0.5073680945314347</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5001994721135852</v>
+        <v>0.5073680945314347</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.4993190214047445</v>
+        <v>0.5147018414582841</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5011705919649646</v>
+        <v>0.5024036923034911</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5011705919649646</v>
+        <v>0.495769057800405</v>
       </c>
     </row>
   </sheetData>
